--- a/financial_models/opportunities/not_monitored/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/not_monitored/3690.HK_Valuation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\not_monitored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0987339-D2F5-4E5D-BEB7-F06913E97688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF480C4-301A-4552-A3A4-048D1095BB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>9.507630003694828E-2</v>
+        <v>1.2208423049346452E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>120.48672858660103</v>
+        <v>95.151560193269901</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>55.523838058341504</v>
+        <v>43.848645250354807</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>69.595222288289435</v>
+        <v>54.961190003332817</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>86.360114934800009</v>
+        <v>68.200869680099785</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>97.666879076801266</v>
+        <v>77.130120739277274</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>326.16 HKD</v>
+        <v>251.02 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.28247914511541944</v>
+        <v>-0.27628214511277988</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>216.22 HKD</v>
+        <v>167.86 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.17709954060827571</v>
+        <v>-0.17239232062213003</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>95.35 HKD</v>
+        <v>76.12 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>8.1124369852861047E-2</v>
+        <v>7.7200288038073744E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>64.22 HKD</v>
+        <v>52.37 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23333800334262822</v>
+        <v>0.22020794486684639</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.21 HKD</v>
+        <v>37.03 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6461,17 +6461,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.39679262071315302</v>
+        <v>0.36971272439319591</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>120.48672858660103</v>
+        <v>95.151560193269901</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6586,11 +6586,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>55.523838058341504</v>
+        <v>43.848645250354807</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>55.523838058341504</v>
+        <v>43.848645250354807</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6607,11 +6607,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>69.595222288289435</v>
+        <v>54.961190003332817</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>69.595222288289435</v>
+        <v>54.961190003332817</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6654,11 +6654,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>86.360114934800009</v>
+        <v>68.200869680099785</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>86.360114934800009</v>
+        <v>68.200869680099785</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,11 +6675,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>97.666879076801266</v>
+        <v>77.130120739277274</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>97.666879076801266</v>
+        <v>77.130120739277274</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>412</v>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>191.07542787795677</v>
+        <v>148.81128323676523</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16951,11 +16951,11 @@
       </c>
       <c r="E28" s="299">
         <f t="shared" si="6"/>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="F28" s="277">
         <f t="shared" si="7"/>
-        <v>132129407.82709648</v>
+        <v>99097055.870322347</v>
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
@@ -16963,15 +16963,15 @@
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>99097055.870322362</v>
+        <v>74322791.90274176</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
-        <v>1.9739040748883379</v>
+        <v>1.2304280561662528</v>
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
-        <v>8.1887809309554596E-2</v>
+        <v>6.1415856982165937E-2</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>56608590.972610578</v>
+        <v>42456443.22945793</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -17000,11 +17000,11 @@
       </c>
       <c r="E29" s="299">
         <f t="shared" si="6"/>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="F29" s="277">
         <f t="shared" si="7"/>
-        <v>144351378.05110291</v>
+        <v>108263533.53832716</v>
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>108263533.53832719</v>
+        <v>81197650.153745368</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
@@ -17020,7 +17020,7 @@
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>8.1887809309554596E-2</v>
+        <v>6.1415856982165937E-2</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -17028,7 +17028,7 @@
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>57664229.032705881</v>
+        <v>43248171.774529397</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -17049,11 +17049,11 @@
       </c>
       <c r="E30" s="299">
         <f t="shared" si="6"/>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="F30" s="277">
         <f t="shared" si="7"/>
-        <v>157703880.52082992</v>
+        <v>118277910.39062244</v>
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
@@ -17061,15 +17061,15 @@
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>118277910.39062244</v>
+        <v>88708432.792966828</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
-        <v>9.2499999999999805E-2</v>
+        <v>9.2500000000000249E-2</v>
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
-        <v>8.1887809309554582E-2</v>
+        <v>6.1415856982165937E-2</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>58739552.651031397</v>
+        <v>44054664.488273546</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -17098,11 +17098,11 @@
       </c>
       <c r="E31" s="299">
         <f t="shared" si="6"/>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="F31" s="277">
         <f t="shared" si="7"/>
-        <v>172291489.46900669</v>
+        <v>129218617.10175501</v>
       </c>
       <c r="G31" s="299">
         <f t="shared" si="2"/>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="H31" s="277">
         <f t="shared" si="8"/>
-        <v>129218617.10175502</v>
+        <v>96913962.826316252</v>
       </c>
       <c r="I31" s="299">
         <f t="shared" si="9"/>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="J31" s="299">
         <f t="shared" si="10"/>
-        <v>8.1887809309554596E-2</v>
+        <v>6.1415856982165937E-2</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="L31" s="277">
         <f t="shared" si="4"/>
-        <v>59834928.924244113</v>
+        <v>44876196.693183072</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -17147,11 +17147,11 @@
       </c>
       <c r="E32" s="299">
         <f t="shared" si="6"/>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="F32" s="277">
         <f t="shared" si="7"/>
-        <v>188228452.24488983</v>
+        <v>141171339.18366736</v>
       </c>
       <c r="G32" s="299">
         <f t="shared" si="2"/>
@@ -17159,15 +17159,15 @@
       </c>
       <c r="H32" s="277">
         <f t="shared" si="8"/>
-        <v>141171339.18366736</v>
+        <v>105878504.38775052</v>
       </c>
       <c r="I32" s="299">
         <f t="shared" si="9"/>
-        <v>9.2500000000000027E-2</v>
+        <v>9.2500000000000249E-2</v>
       </c>
       <c r="J32" s="299">
         <f t="shared" si="10"/>
-        <v>8.1887809309554582E-2</v>
+        <v>6.1415856982165937E-2</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
@@ -17175,7 +17175,7 @@
       </c>
       <c r="L32" s="277">
         <f t="shared" si="4"/>
-        <v>60950731.794626273</v>
+        <v>45713048.845969707</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -17196,11 +17196,11 @@
       </c>
       <c r="E33" s="299">
         <f t="shared" si="6"/>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="F33" s="277">
         <f t="shared" si="7"/>
-        <v>205639584.07754216</v>
+        <v>154229688.05815661</v>
       </c>
       <c r="G33" s="299">
         <f t="shared" si="2"/>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="H33" s="277">
         <f t="shared" si="8"/>
-        <v>154229688.05815661</v>
+        <v>115672266.04361746</v>
       </c>
       <c r="I33" s="299">
         <f t="shared" si="9"/>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="J33" s="299">
         <f t="shared" si="10"/>
-        <v>8.1887809309554596E-2</v>
+        <v>6.1415856982165944E-2</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
@@ -17224,7 +17224,7 @@
       </c>
       <c r="L33" s="277">
         <f t="shared" si="4"/>
-        <v>62087342.177742846</v>
+        <v>46565506.633307137</v>
       </c>
       <c r="N33" s="275"/>
       <c r="O33" s="275"/>
@@ -17253,11 +17253,11 @@
       </c>
       <c r="E34" s="299">
         <f t="shared" si="6"/>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="F34" s="277">
         <f t="shared" si="7"/>
-        <v>224661245.60471481</v>
+        <v>168495934.20353609</v>
       </c>
       <c r="G34" s="299">
         <f t="shared" si="2"/>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="H34" s="277">
         <f t="shared" si="8"/>
-        <v>168495934.20353609</v>
+        <v>126371950.65265207</v>
       </c>
       <c r="I34" s="299">
         <f t="shared" si="9"/>
@@ -17273,7 +17273,7 @@
       </c>
       <c r="J34" s="299">
         <f t="shared" si="10"/>
-        <v>8.1887809309554582E-2</v>
+        <v>6.1415856982165944E-2</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="L34" s="277">
         <f t="shared" si="4"/>
-        <v>63245148.092479318</v>
+        <v>47433861.069359489</v>
       </c>
       <c r="N34" s="275"/>
       <c r="O34" s="275"/>
@@ -17310,11 +17310,11 @@
       </c>
       <c r="E35" s="299">
         <f t="shared" si="6"/>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="F35" s="277">
         <f t="shared" si="7"/>
-        <v>245442410.82315093</v>
+        <v>184081808.11736318</v>
       </c>
       <c r="G35" s="299">
         <f t="shared" si="2"/>
@@ -17322,15 +17322,15 @@
       </c>
       <c r="H35" s="277">
         <f t="shared" si="8"/>
-        <v>184081808.11736321</v>
+        <v>138061356.08802238</v>
       </c>
       <c r="I35" s="299">
         <f t="shared" si="9"/>
-        <v>9.2500000000000249E-2</v>
+        <v>9.2500000000000027E-2</v>
       </c>
       <c r="J35" s="299">
         <f t="shared" si="10"/>
-        <v>8.1887809309554596E-2</v>
+        <v>6.141585698216593E-2</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="L35" s="277">
         <f t="shared" si="4"/>
-        <v>64424544.793504588</v>
+        <v>48318408.595128432</v>
       </c>
       <c r="N35" s="275"/>
       <c r="O35" s="275"/>
@@ -18134,11 +18134,11 @@
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>250351259.03961393</v>
+        <v>187763444.27971044</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18146,11 +18146,11 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>2589840610.7546268</v>
+        <v>1942380458.0659704</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
-        <v>1.9999999999999796E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="J51" s="454"/>
       <c r="K51" s="119">
@@ -18159,7 +18159,7 @@
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>906386699.16378844</v>
+        <v>679790024.37284148</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18172,7 +18172,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>1498009144.3660705</v>
+        <v>1150523702.4653873</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18196,7 +18196,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>1498009144.3660705</v>
+        <v>1150523702.4653873</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18231,19 +18231,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>372109095.78911704</v>
+        <v>281449093.24269783</v>
       </c>
       <c r="C56" s="118">
-        <v>381411823.18384486</v>
+        <v>288485320.57376528</v>
       </c>
       <c r="D56" s="118">
-        <v>390714550.57857287</v>
+        <v>295521547.90483284</v>
       </c>
       <c r="E56" s="118">
-        <v>409320005.3680287</v>
+        <v>309594002.56696767</v>
       </c>
       <c r="F56" s="118">
-        <v>418622732.76275671</v>
+        <v>316630229.89803517</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18257,19 +18257,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>371628426.64082944</v>
+        <v>281088591.38148218</v>
       </c>
       <c r="C57" s="118">
-        <v>390199470.42093325</v>
+        <v>295076056.00158155</v>
       </c>
       <c r="D57" s="118">
-        <v>409223213.37733388</v>
+        <v>309403045.00390351</v>
       </c>
       <c r="E57" s="118">
-        <v>448628796.81902522</v>
+        <v>339075596.15521502</v>
       </c>
       <c r="F57" s="118">
-        <v>469010637.30431598</v>
+        <v>354421158.30420458</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18283,19 +18283,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>371180250.2787897</v>
+        <v>280752459.10995239</v>
       </c>
       <c r="C58" s="118">
-        <v>408319821.67644751</v>
+        <v>308725501.22823876</v>
       </c>
       <c r="D58" s="118">
-        <v>447693276.95813382</v>
+        <v>338373956.25954658</v>
       </c>
       <c r="E58" s="118">
-        <v>533395097.45403737</v>
+        <v>402887048.77156019</v>
       </c>
       <c r="F58" s="118">
-        <v>579850091.80847764</v>
+        <v>437846658.10743332</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18309,19 +18309,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>370762370.22094381</v>
+        <v>280439049.06656796</v>
       </c>
       <c r="C59" s="118">
-        <v>416542081.1416024</v>
+        <v>314892195.82710493</v>
       </c>
       <c r="D59" s="118">
-        <v>466278270.98235142</v>
+        <v>352312701.77770966</v>
       </c>
       <c r="E59" s="118">
-        <v>578504702.13153017</v>
+        <v>436719252.27967972</v>
       </c>
       <c r="F59" s="118">
-        <v>641452009.43471754</v>
+        <v>484048096.32711315</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18335,19 +18335,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>355168265.2966283</v>
+        <v>270950716.43473935</v>
       </c>
       <c r="C60" s="118">
-        <v>417745975.96630043</v>
+        <v>318228605.72833085</v>
       </c>
       <c r="D60" s="118">
-        <v>488650118.24824762</v>
+        <v>371762354.96143556</v>
       </c>
       <c r="E60" s="118">
-        <v>658640891.12304354</v>
+        <v>499999828.35174233</v>
       </c>
       <c r="F60" s="118">
-        <v>759449421.61352849</v>
+        <v>575994977.4321717</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18361,19 +18361,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>354804972.28444433</v>
+        <v>270678246.67560136</v>
       </c>
       <c r="C61" s="118">
-        <v>425439224.1006819</v>
+        <v>323998541.82911694</v>
       </c>
       <c r="D61" s="118">
-        <v>507311758.29408193</v>
+        <v>385758584.99581128</v>
       </c>
       <c r="E61" s="118">
-        <v>710407337.22954416</v>
+        <v>538824662.93161774</v>
       </c>
       <c r="F61" s="118">
-        <v>834761072.09306312</v>
+        <v>632478715.29182243</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18387,19 +18387,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>340289572.58194351</v>
+        <v>261849735.18442094</v>
       </c>
       <c r="C62" s="118">
-        <v>426456465.57658786</v>
+        <v>327143909.50652432</v>
       </c>
       <c r="D62" s="118">
-        <v>530735746.26027912</v>
+        <v>406065824.92871946</v>
       </c>
       <c r="E62" s="118">
-        <v>806224259.06487751</v>
+        <v>614243644.46579909</v>
       </c>
       <c r="F62" s="118">
-        <v>984751359.44376838</v>
+        <v>748991036.83159995</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18413,19 +18413,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>339973735.99145859</v>
+        <v>261612857.74155724</v>
       </c>
       <c r="C63" s="118">
-        <v>433654738.40025479</v>
+        <v>332542614.12427449</v>
       </c>
       <c r="D63" s="118">
-        <v>549474348.42213547</v>
+        <v>420119776.55011177</v>
       </c>
       <c r="E63" s="118">
-        <v>865629899.20861125</v>
+        <v>658797874.57359946</v>
       </c>
       <c r="F63" s="118">
-        <v>1076823894.1392722</v>
+        <v>818045437.85322762</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18439,19 +18439,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>326460914.033705</v>
+        <v>253397158.08974105</v>
       </c>
       <c r="C64" s="118">
-        <v>434499626.42931652</v>
+        <v>335508735.52975541</v>
       </c>
       <c r="D64" s="118">
-        <v>573979428.44289804</v>
+        <v>441308072.67671973</v>
       </c>
       <c r="E64" s="118">
-        <v>979899852.88760972</v>
+        <v>748479405.74354053</v>
       </c>
       <c r="F64" s="118">
-        <v>1266875860.663126</v>
+        <v>965269268.25514877</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18465,19 +18465,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>326186334.70367754</v>
+        <v>253191223.59222049</v>
       </c>
       <c r="C65" s="118">
-        <v>441234770.12140387</v>
+        <v>340560093.29882097</v>
       </c>
       <c r="D65" s="118">
-        <v>592795310.11878014</v>
+        <v>455419983.93363142</v>
       </c>
       <c r="E65" s="118">
-        <v>1048072005.8228612</v>
+        <v>799608520.44497907</v>
       </c>
       <c r="F65" s="118">
-        <v>1379439475.8710871</v>
+        <v>1049691979.6611197</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18491,19 +18491,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>290536748.84018481</v>
+        <v>231466964.94902861</v>
       </c>
       <c r="C66" s="277">
-        <v>455062338.5164063</v>
+        <v>357638624.66209</v>
       </c>
       <c r="D66" s="118">
-        <v>710962867.45403194</v>
+        <v>552913774.7866087</v>
       </c>
       <c r="E66" s="118">
-        <v>1704747531.1229229</v>
+        <v>1307122202.3846078</v>
       </c>
       <c r="F66" s="118">
-        <v>2608671833.2677984</v>
+        <v>1990857430.50455</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18526,19 +18526,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>270442975.65256286</v>
+        <v>219199254.84457648</v>
       </c>
       <c r="C67" s="277">
-        <v>471017190.6401341</v>
+        <v>373845406.9819231</v>
       </c>
       <c r="D67" s="118">
-        <v>827853817.48771203</v>
+        <v>646879526.96745467</v>
       </c>
       <c r="E67" s="118">
-        <v>2555179148.7410131</v>
+        <v>1958159587.068953</v>
       </c>
       <c r="F67" s="118">
-        <v>4449135120.4146099</v>
+        <v>3389924879.7811742</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18561,19 +18561,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>245552894.87864643</v>
+        <v>204064381.59867322</v>
       </c>
       <c r="C68" s="277">
-        <v>479667794.09764963</v>
+        <v>386366503.16232318</v>
       </c>
       <c r="D68" s="118">
-        <v>965388159.71379519</v>
+        <v>760095164.12431884</v>
       </c>
       <c r="E68" s="118">
-        <v>4012229431.7812252</v>
+        <v>3077262986.0418406</v>
       </c>
       <c r="F68" s="118">
-        <v>8131693557.0344124</v>
+        <v>6193224168.4030266</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18596,19 +18596,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>231556510.58738506</v>
+        <v>195542141.49229324</v>
       </c>
       <c r="C69" s="277">
-        <v>490309361.11384761</v>
+        <v>398161775.36536586</v>
       </c>
       <c r="D69" s="118">
-        <v>1096717705.205266</v>
+        <v>865739719.04005134</v>
       </c>
       <c r="E69" s="118">
-        <v>5836951651.2216959</v>
+        <v>4468975568.1147928</v>
       </c>
       <c r="F69" s="118">
-        <v>13474778779.959995</v>
+        <v>10240797646.328701</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18736,23 +18736,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>54.133856328085692</v>
+        <v>43.107013189466358</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>55.26533341678838</v>
+        <v>43.962819199703567</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>56.396810505491096</v>
+        <v>44.818625209940798</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>58.659764682896494</v>
+        <v>46.530237230415224</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>59.791241771599204</v>
+        <v>47.386043240652455</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18767,23 +18767,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>54.075393244577313</v>
+        <v>43.063165876835079</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>56.334162061385882</v>
+        <v>44.764440683151697</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>58.647992015033175</v>
+        <v>46.50701134209735</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>63.440835332843868</v>
+        <v>50.116040217875756</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>65.919848697007268</v>
+        <v>51.982498434708511</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18798,23 +18798,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>54.020882211003062</v>
+        <v>43.022282601654389</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>58.53811380745973</v>
+        <v>46.424602686417273</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>63.32704942429141</v>
+        <v>50.030700786461423</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>73.750836152276293</v>
+        <v>57.877333607290851</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>79.401088980027765</v>
+        <v>62.129419615524817</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18829,23 +18829,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.970056072472296</v>
+        <v>42.984162997756314</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>59.53817516661168</v>
+        <v>47.17464870578123</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>65.587514988830705</v>
+        <v>51.726049959865882</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>79.237451206904794</v>
+        <v>61.99229489826223</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>86.893639869323181</v>
+        <v>67.748832782496365</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18860,23 +18860,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>52.073367962414558</v>
+        <v>41.830111016292413</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>59.684603128386151</v>
+        <v>47.580451348552145</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>68.308569958974559</v>
+        <v>54.091682749779864</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>88.984298338127118</v>
+        <v>69.689018552233307</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>101.24549204572874</v>
+        <v>78.932197072737154</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18891,23 +18891,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>52.029181166184785</v>
+        <v>41.796970919120085</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>60.62032161527749</v>
+        <v>48.282240213720648</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>70.578357866706298</v>
+        <v>55.794023680578675</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>95.280575252170948</v>
+        <v>74.411226237766172</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>110.40553763389373</v>
+        <v>85.802231263860875</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18923,23 +18923,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>50.263694390118509</v>
+        <v>40.723172015233011</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>60.74404720400301</v>
+        <v>48.664806671010304</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>73.427383167052099</v>
+        <v>58.263963488972486</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>106.93464692024307</v>
+        <v>83.584326344685309</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>128.64863629348</v>
+        <v>99.973454044024479</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18954,23 +18954,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>50.225279648855619</v>
+        <v>40.694360959285838</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>61.619562569832844</v>
+        <v>49.32144319538267</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>75.706531864075217</v>
+        <v>59.973325011739824</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>114.16006780062328</v>
+        <v>89.003392004970451</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>139.8472836456304</v>
+        <v>108.37243955813726</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18986,23 +18986,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>48.581734933401322</v>
+        <v>39.695097460608991</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>61.722325061609638</v>
+        <v>49.682208191518569</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>78.687048805379192</v>
+        <v>62.550426392727481</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>128.05855466676314</v>
+        <v>99.911225105193552</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>162.96302558454832</v>
+        <v>126.27905811660763</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19018,23 +19018,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>48.548338252215807</v>
+        <v>39.670049949719861</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>62.541510710437336</v>
+        <v>50.29659742813935</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>80.975596896347341</v>
+        <v>64.266837460953596</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>136.35023364012397</v>
+        <v>106.12998433521419</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>176.653973005144</v>
+        <v>136.54726868205438</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19050,23 +19050,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>44.212331410916612</v>
+        <v>37.027760233936768</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>64.22333757341535</v>
+        <v>52.37383414875751</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>95.348143578578728</v>
+        <v>76.124864248176578</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>216.22071463582785</v>
+        <v>167.85812909878908</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>326.16370171917839</v>
+        <v>251.01984205998622</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19082,23 +19082,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>41.768355249660118</v>
+        <v>35.53565664699294</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>66.163902836229383</v>
+        <v>54.34504131181761</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>109.56541838712097</v>
+        <v>87.553780866285479</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>319.65746495795076</v>
+        <v>247.04285132086886</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>550.0165519258012</v>
+        <v>421.18636390210304</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19114,23 +19114,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>38.741011231430967</v>
+        <v>33.694824212424983</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>67.216063046919658</v>
+        <v>55.867963875537427</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>126.2935187103446</v>
+        <v>101.32403276020507</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>496.87635382726188</v>
+        <v>383.15775634804919</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>997.92073336032604</v>
+        <v>762.1475447757656</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19146,23 +19146,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>37.038651538593406</v>
+        <v>32.658276647862685</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>68.510381235104575</v>
+        <v>57.3026055334579</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>142.26693870731788</v>
+        <v>114.1734250256485</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>718.81464105619955</v>
+        <v>552.42971647957313</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>1647.7923523171955</v>
+        <v>1254.447970316457</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>326.16370171917839</v>
+        <v>251.01984205998622</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19237,7 +19237,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>216.22071463582785</v>
+        <v>167.85812909878908</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19265,7 +19265,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>95.348143578578728</v>
+        <v>76.124864248176578</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19293,7 +19293,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>64.22333757341535</v>
+        <v>52.37383414875751</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>44.212331410916612</v>
+        <v>37.027760233936768</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19681,7 +19681,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>216.22071463582785</v>
+        <v>167.85812909878908</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19705,7 +19705,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>95.348143578578728</v>
+        <v>76.124864248176578</v>
       </c>
       <c r="F23" s="327">
         <v>0.6</v>
@@ -19728,7 +19728,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>64.22333757341535</v>
+        <v>52.37383414875751</v>
       </c>
       <c r="F24" s="327">
         <v>0.2</v>
@@ -19744,7 +19744,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>113.29769658899588</v>
+        <v>89.721311198415265</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>326.16370171917839</v>
+        <v>251.01984205998622</v>
       </c>
       <c r="F29" s="327">
         <v>0.05</v>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>44.212331410916612</v>
+        <v>37.027760233936768</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>9.507630003694828E-2</v>
+        <v>1.2208423049346452E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.54181645949322654</v>
+        <v>0.42514234582660099</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19899,7 +19899,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>120.48672858660103</v>
+        <v>95.151560193269901</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19937,7 +19937,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>401</v>
@@ -20002,7 +20002,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>191.07542787795677</v>
+        <v>148.81128323676523</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>7.3657679016480584E-2</v>
+        <v>9.3269860861465825E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20147,11 +20147,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>55.523838058341504</v>
+        <v>43.848645250354807</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>55.523838058341504</v>
+        <v>43.848645250354807</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20172,11 +20172,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>69.595222288289435</v>
+        <v>54.961190003332817</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>69.595222288289435</v>
+        <v>54.961190003332817</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20218,11 +20218,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>86.360114934800009</v>
+        <v>68.200869680099785</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>86.360114934800009</v>
+        <v>68.200869680099785</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20243,11 +20243,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>97.666879076801266</v>
+        <v>77.130120739277274</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>97.666879076801266</v>
+        <v>77.130120739277274</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20391,7 +20391,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>9.507630003694828E-2</v>
+        <v>1.2208423049346452E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20399,13 +20399,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20469,7 +20469,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>120.48672858660103</v>
+        <v>95.151560193269901</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>55.523838058341504</v>
+        <v>43.848645250354807</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20537,7 +20537,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>69.595222288289435</v>
+        <v>54.961190003332817</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>86.360114934800009</v>
+        <v>68.200869680099785</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>97.666879076801266</v>
+        <v>77.130120739277274</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20590,22 +20590,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20795,10 +20795,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20814,22 +20814,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20900,7 +20900,7 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
@@ -20914,7 +20914,7 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.10918374574607279</v>
+        <v>8.1887809309554582E-2</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
@@ -20964,22 +20964,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20987,13 +20987,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21142,33 +21142,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21231,23 +21231,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21291,13 +21291,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21342,7 +21342,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>326.16 HKD</v>
+        <v>251.02 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21365,7 +21365,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>216.22 HKD</v>
+        <v>167.86 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>95.35 HKD</v>
+        <v>76.12 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>64.22 HKD</v>
+        <v>52.37 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21431,7 +21431,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>44.21 HKD</v>
+        <v>37.03 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21453,7 +21453,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>120.48672858660103</v>
+        <v>95.151560193269901</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21461,13 +21461,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21480,22 +21480,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21560,11 +21560,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>55.523838058341504</v>
+        <v>43.848645250354807</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>55.523838058341504</v>
+        <v>43.848645250354807</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21581,11 +21581,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>69.595222288289435</v>
+        <v>54.961190003332817</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>69.595222288289435</v>
+        <v>54.961190003332817</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21621,11 +21621,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>86.360114934800009</v>
+        <v>68.200869680099785</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>86.360114934800009</v>
+        <v>68.200869680099785</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21642,11 +21642,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>97.666879076801266</v>
+        <v>77.130120739277274</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>97.666879076801266</v>
+        <v>77.130120739277274</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21664,13 +21664,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21678,13 +21678,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21721,22 +21721,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21760,15 +21760,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21783,12 +21780,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
